--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>91976</v>
+        <v>92004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92011</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92022</v>
+        <v>92025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25936-2025 artfynd.xlsx
+++ b/artfynd/A 25936-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129581729</v>
       </c>
       <c r="B2" t="n">
-        <v>92025</v>
+        <v>92028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
